--- a/sheets/민요/검수/천안 삼거리 (굿거리).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (굿거리).xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I30" s="2"/>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2388,12 +2388,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="I54" s="2"/>
@@ -2731,12 +2731,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I60" s="2"/>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I61" s="2"/>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I72" s="2"/>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -3496,7 +3496,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -3506,13 +3506,13 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -3522,13 +3522,13 @@
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="L7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
@@ -3798,13 +3798,13 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E13" s="9"/>
@@ -3816,19 +3816,19 @@
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="M13" s="9"/>
@@ -3839,13 +3839,13 @@
       <c r="C14" s="10"/>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="10"/>
@@ -3857,7 +3857,7 @@
       <c r="I14" s="10"/>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="10"/>

--- a/sheets/민요/검수/천안 삼거리 (굿거리).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (굿거리).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3231,81 +3272,81 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">천안 삼거리</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">척</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">천</t>
         </is>
@@ -3313,62 +3354,62 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">멋</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
@@ -3376,117 +3417,117 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="18" t="inlineStr">
+      <c r="K5" s="27"/>
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M5" s="13"/>
+      <c r="M5" s="28"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">났</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">졌</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">겨</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -3494,54 +3535,54 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="26"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="26"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
@@ -3549,62 +3590,62 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -3612,62 +3653,62 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3675,120 +3716,120 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="26"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="26"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="26"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="26"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="26"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M10" s="9"/>
+      <c r="M10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南無南</t>
         </is>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="C11" s="28"/>
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南無南</t>
         </is>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="E11" s="28"/>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南無南</t>
         </is>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="28"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="I11" s="27"/>
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南無南</t>
         </is>
       </c>
-      <c r="K11" s="13"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="28"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M11" s="10"/>
+      <c r="M11" s="27"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3796,77 +3837,77 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="26"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="26"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="26"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="26"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="26"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
+      <c r="M13" s="26"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="B14" s="21"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="27"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
+      <c r="M14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/천안 삼거리 (굿거리).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (굿거리).xlsx
@@ -3253,24 +3253,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="29.14" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="29.14" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="29.14" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="29.14" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="M5" s="28"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="29.14" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="29.14" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="29.14" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="29.14" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3714,35 +3714,35 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="29.14" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="26"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="26"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="26"/>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="29.14" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       <c r="G11" s="28"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="27"/>
@@ -3787,12 +3787,12 @@
       <c r="K11" s="28"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M11" s="27"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="29.14" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
       <c r="E13" s="26"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G13" s="26"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="M13" s="26"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="27"/>

--- a/sheets/민요/검수/천안 삼거리 (굿거리).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (굿거리).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3296,7 +3319,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
@@ -3306,7 +3329,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -3316,7 +3339,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">척</t>
         </is>
@@ -3326,7 +3349,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
@@ -3336,7 +3359,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
@@ -3346,7 +3369,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">천</t>
         </is>
@@ -3359,7 +3382,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
@@ -3369,7 +3392,7 @@
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -3379,7 +3402,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
@@ -3389,7 +3412,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="26" t="inlineStr">
+      <c r="I4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">멋</t>
         </is>
@@ -3399,7 +3422,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="K4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -3409,7 +3432,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
@@ -3422,7 +3445,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -3432,7 +3455,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
@@ -3442,7 +3465,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3452,7 +3475,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -3462,13 +3485,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K5" s="27"/>
+      <c r="K5" s="33"/>
       <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M5" s="28"/>
+      <c r="M5" s="34"/>
     </row>
     <row r="6" ht="29.14" customHeight="1">
       <c r="A6" s="0"/>
@@ -3477,7 +3500,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">났</t>
         </is>
@@ -3487,7 +3510,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -3497,7 +3520,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">졌</t>
         </is>
@@ -3507,7 +3530,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">겨</t>
         </is>
@@ -3517,7 +3540,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
@@ -3527,7 +3550,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -3540,7 +3563,7 @@
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -3550,13 +3573,13 @@
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="E7" s="26"/>
+      <c r="E7" s="32"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -3566,13 +3589,13 @@
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="I7" s="26"/>
+      <c r="I7" s="32"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="K7" s="26" t="inlineStr">
+      <c r="K7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -3582,7 +3605,7 @@
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="M7" s="26" t="inlineStr">
+      <c r="M7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
@@ -3595,7 +3618,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -3605,7 +3628,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -3615,7 +3638,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -3625,7 +3648,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
@@ -3635,7 +3658,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="27" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -3645,7 +3668,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M8" s="27" t="inlineStr">
+      <c r="M8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -3658,7 +3681,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3668,7 +3691,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3678,7 +3701,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3688,7 +3711,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -3698,7 +3721,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3708,7 +3731,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3721,37 +3744,37 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C10" s="26"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="26"/>
+      <c r="E10" s="32"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="26"/>
+      <c r="I10" s="32"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K10" s="26"/>
+      <c r="K10" s="32"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M10" s="26"/>
+      <c r="M10" s="32"/>
     </row>
     <row r="11" ht="29.14" customHeight="1">
       <c r="A11" s="0"/>
@@ -3760,37 +3783,37 @@
           <t xml:space="preserve">南無南</t>
         </is>
       </c>
-      <c r="C11" s="28"/>
+      <c r="C11" s="34"/>
       <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南無南</t>
         </is>
       </c>
-      <c r="E11" s="28"/>
+      <c r="E11" s="34"/>
       <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南無南</t>
         </is>
       </c>
-      <c r="G11" s="28"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="27"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南無南</t>
         </is>
       </c>
-      <c r="K11" s="28"/>
+      <c r="K11" s="34"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M11" s="27"/>
+      <c r="M11" s="33"/>
     </row>
     <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
@@ -3799,37 +3822,37 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="29"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="29"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K12" s="22"/>
+      <c r="K12" s="29"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
@@ -3842,72 +3865,72 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="26"/>
+      <c r="C13" s="32"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="26"/>
+      <c r="E13" s="32"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="32"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="I13" s="26"/>
+      <c r="I13" s="32"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="26"/>
+      <c r="K13" s="32"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="M13" s="26"/>
+      <c r="M13" s="32"/>
     </row>
     <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
-      <c r="C14" s="27"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I14" s="27"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/천안 삼거리 (굿거리).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (굿거리).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,9 +224,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -241,22 +233,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -353,7 +330,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">71</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
     </row>
@@ -365,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
@@ -425,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">머리 "천안 삼거리 \"굿거리\"". 12정간, 굵은 선 3칸마다(굿거리 3/4). 6줄 사용. 각 율명열 오른쪽 가사 칸 전사: 1줄 천안(삼)거리, 2줄 능수(버)들은, 3줄 제멋에겨(워)서, 4줄 척늘어졌구나, 5줄 에구와(에루화)좋(다), 6줄 성해가(났)구나. 후렴 "흥"은 각 줄 7정간(1줄은 10정간에도)에 적음. 9정간의 南無南은 한 칸에 세로로 쌓여 쓴 세 글자. 1줄 6정간 율명 왼쪽에 먹칠 번짐 있음. AI 재판독.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 머리 "천안삼거리 "굿거리"". 손으로 그린 격자 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽부터 6줄 사용(왼쪽 빈 줄 제외). 가사는 각 율명 줄 오른쪽 칸. 7정간 흥·10정간 응은 후렴 입타령. 9정간 南|無|南, 12정간 潢|無 는 한 정간에 세로로 쌓여 쓰임. 줄6 6정간 아래 먹칠 번짐.</t>
         </is>
       </c>
     </row>
@@ -702,7 +679,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3정간 가사칸에 쉼표(,) 비슷한 표시</t>
+          <t xml:space="preserve">가사 칸에 쉼표(,) 모양 점</t>
         </is>
       </c>
       <c r="K4" s="2"/>
@@ -921,12 +898,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="2"/>
@@ -966,7 +943,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">흥</t>
+          <t xml:space="preserve">응</t>
         </is>
       </c>
       <c r="J11" s="4"/>
@@ -1030,12 +1007,13 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I13" s="2"/>
@@ -1151,7 +1129,11 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I16" s="2"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
       <c r="J16" s="4"/>
       <c r="K16" s="2"/>
     </row>
@@ -1256,12 +1238,13 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲
+姑</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1327,22 +1310,28 @@
         <v>2</v>
       </c>
       <c r="E21" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" s="2">
         <v>3</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南|無|南</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I21" s="2"/>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥</t>
+        </is>
+      </c>
       <c r="J21" s="4"/>
       <c r="K21" s="2"/>
     </row>
@@ -1362,27 +1351,23 @@
         <v>2</v>
       </c>
       <c r="E22" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22" s="2">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南無南</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南無南</t>
-        </is>
-      </c>
-      <c r="I22" s="3"/>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한 정간에 南·無·南 세로로 쌓여 쓰임</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="4"/>
       <c r="K22" s="2"/>
     </row>
     <row r="23">
@@ -1401,19 +1386,19 @@
         <v>2</v>
       </c>
       <c r="E23" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23" s="2">
         <v>4</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I23" s="2"/>
@@ -1436,19 +1421,20 @@
         <v>2</v>
       </c>
       <c r="E24" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F24" s="2">
         <v>4</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1465,28 +1451,32 @@
         </is>
       </c>
       <c r="C25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I25" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제</t>
+        </is>
+      </c>
       <c r="J25" s="4"/>
       <c r="K25" s="2"/>
     </row>
@@ -1506,7 +1496,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="2">
         <v>1</v>
@@ -1523,7 +1513,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">제</t>
+          <t xml:space="preserve">멋</t>
         </is>
       </c>
       <c r="J26" s="4"/>
@@ -1545,7 +1535,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="2">
         <v>1</v>
@@ -1562,7 +1552,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">멋</t>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J27" s="4"/>
@@ -1584,10 +1574,10 @@
         <v>3</v>
       </c>
       <c r="E28" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1591,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에</t>
+          <t xml:space="preserve">겨</t>
         </is>
       </c>
       <c r="J28" s="4"/>
@@ -1623,26 +1613,22 @@
         <v>3</v>
       </c>
       <c r="E29" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="2">
         <v>2</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겨</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–無</t>
+        </is>
+      </c>
+      <c r="I29" s="2"/>
       <c r="J29" s="4"/>
       <c r="K29" s="2"/>
     </row>
@@ -1662,23 +1648,31 @@
         <v>3</v>
       </c>
       <c r="E30" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F30" s="2">
         <v>2</v>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–無</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–無</t>
-        </is>
-      </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="4"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">워</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">氵+姑로 보임(潢 아님). 가사 워 위에 동그라미 덧씀</t>
+        </is>
+      </c>
       <c r="K30" s="2"/>
     </row>
     <row r="31">
@@ -1697,10 +1691,10 @@
         <v>3</v>
       </c>
       <c r="E31" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -1714,7 +1708,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">워</t>
+          <t xml:space="preserve">서</t>
         </is>
       </c>
       <c r="J31" s="4"/>
@@ -1736,27 +1730,27 @@
         <v>3</v>
       </c>
       <c r="E32" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32" s="2">
         <v>3</v>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
-      <c r="J32" s="4"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작은 삐침 하나, – 추정</t>
+        </is>
+      </c>
       <c r="K32" s="2"/>
     </row>
     <row r="33">
@@ -1775,23 +1769,31 @@
         <v>3</v>
       </c>
       <c r="E33" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F33" s="2">
-        <v>3</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 어/이</t>
+        </is>
+      </c>
       <c r="K33" s="2"/>
     </row>
     <row r="34">
@@ -1810,19 +1812,19 @@
         <v>3</v>
       </c>
       <c r="E34" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I34" s="2"/>
@@ -1845,19 +1847,20 @@
         <v>3</v>
       </c>
       <c r="E35" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F35" s="2">
         <v>4</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I35" s="2"/>
@@ -1874,29 +1877,37 @@
         </is>
       </c>
       <c r="C36" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2">
-        <v>4</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–無</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–無</t>
-        </is>
-      </c>
-      <c r="I36" s="2"/>
-      <c r="J36" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">축</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 축으로 쓰임(척 의도?)</t>
+        </is>
+      </c>
       <c r="K36" s="2"/>
     </row>
     <row r="37">
@@ -1909,28 +1920,32 @@
         </is>
       </c>
       <c r="C37" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F37" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="I37" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">늘</t>
+        </is>
+      </c>
       <c r="J37" s="4"/>
       <c r="K37" s="2"/>
     </row>
@@ -1950,31 +1965,27 @@
         <v>4</v>
       </c>
       <c r="E38" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" s="2">
         <v>1</v>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">척</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 축/척</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J38" s="4"/>
       <c r="K38" s="2"/>
     </row>
     <row r="39">
@@ -1993,24 +2004,24 @@
         <v>4</v>
       </c>
       <c r="E39" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F39" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">늘</t>
+          <t xml:space="preserve">졌</t>
         </is>
       </c>
       <c r="J39" s="4"/>
@@ -2032,24 +2043,24 @@
         <v>4</v>
       </c>
       <c r="E40" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">어</t>
+          <t xml:space="preserve">구</t>
         </is>
       </c>
       <c r="J40" s="4"/>
@@ -2071,24 +2082,25 @@
         <v>4</v>
       </c>
       <c r="E41" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F41" s="2">
         <v>2</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">仲|潢</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">仲
+潢</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">졌</t>
+          <t xml:space="preserve">나</t>
         </is>
       </c>
       <c r="J41" s="4"/>
@@ -2110,24 +2122,24 @@
         <v>4</v>
       </c>
       <c r="E42" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F42" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구</t>
+          <t xml:space="preserve">흥</t>
         </is>
       </c>
       <c r="J42" s="4"/>
@@ -2149,26 +2161,24 @@
         <v>4</v>
       </c>
       <c r="E43" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F43" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南|無|南</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I43" s="2"/>
       <c r="J43" s="4"/>
       <c r="K43" s="2"/>
     </row>
@@ -2188,10 +2198,10 @@
         <v>4</v>
       </c>
       <c r="E44" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F44" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -2205,7 +2215,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">흥</t>
+          <t xml:space="preserve">응</t>
         </is>
       </c>
       <c r="J44" s="4"/>
@@ -2221,28 +2231,32 @@
         </is>
       </c>
       <c r="C45" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F45" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I45" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="J45" s="4"/>
       <c r="K45" s="2"/>
     </row>
@@ -2256,33 +2270,33 @@
         </is>
       </c>
       <c r="C46" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F46" s="2">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南無南</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南無南</t>
-        </is>
-      </c>
-      <c r="I46" s="3"/>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한 정간에 南·無·南 세로로 쌓여 쓰임</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–南</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–南</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">루</t>
+        </is>
+      </c>
+      <c r="J46" s="4"/>
       <c r="K46" s="2"/>
     </row>
     <row r="47">
@@ -2295,16 +2309,16 @@
         </is>
       </c>
       <c r="C47" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F47" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -2316,7 +2330,11 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I47" s="2"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
+        </is>
+      </c>
       <c r="J47" s="4"/>
       <c r="K47" s="2"/>
     </row>
@@ -2330,28 +2348,32 @@
         </is>
       </c>
       <c r="C48" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F48" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I48" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
       <c r="J48" s="4"/>
       <c r="K48" s="2"/>
     </row>
@@ -2365,25 +2387,25 @@
         </is>
       </c>
       <c r="C49" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F49" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2406,24 +2428,24 @@
         <v>5</v>
       </c>
       <c r="E50" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F50" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에</t>
+          <t xml:space="preserve">다</t>
         </is>
       </c>
       <c r="J50" s="4"/>
@@ -2445,24 +2467,24 @@
         <v>5</v>
       </c>
       <c r="E51" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F51" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–南</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–南</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구</t>
+          <t xml:space="preserve">흥</t>
         </is>
       </c>
       <c r="J51" s="4"/>
@@ -2484,31 +2506,23 @@
         <v>5</v>
       </c>
       <c r="E52" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F52" s="2">
-        <v>1</v>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">와</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 와/화</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I52" s="2"/>
+      <c r="J52" s="4"/>
       <c r="K52" s="2"/>
     </row>
     <row r="53">
@@ -2527,26 +2541,22 @@
         <v>5</v>
       </c>
       <c r="E53" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F53" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좋</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I53" s="2"/>
       <c r="J53" s="4"/>
       <c r="K53" s="2"/>
     </row>
@@ -2566,22 +2576,26 @@
         <v>5</v>
       </c>
       <c r="E54" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F54" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–南</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–南</t>
-        </is>
-      </c>
-      <c r="I54" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
       <c r="J54" s="4"/>
       <c r="K54" s="2"/>
     </row>
@@ -2601,26 +2615,22 @@
         <v>5</v>
       </c>
       <c r="E55" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F55" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–無</t>
+        </is>
+      </c>
+      <c r="I55" s="2"/>
       <c r="J55" s="4"/>
       <c r="K55" s="2"/>
     </row>
@@ -2640,26 +2650,23 @@
         <v>5</v>
       </c>
       <c r="E56" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F56" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흥</t>
-        </is>
-      </c>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I56" s="2"/>
       <c r="J56" s="4"/>
       <c r="K56" s="2"/>
     </row>
@@ -2673,28 +2680,32 @@
         </is>
       </c>
       <c r="C57" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D57" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E57" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F57" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I57" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성</t>
+        </is>
+      </c>
       <c r="J57" s="4"/>
       <c r="K57" s="2"/>
     </row>
@@ -2708,33 +2719,33 @@
         </is>
       </c>
       <c r="C58" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D58" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E58" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F58" s="2">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南無南</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南無南</t>
-        </is>
-      </c>
-      <c r="I58" s="3"/>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한 정간에 南·無·南 세로로 쌓여 쓰임</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
+        </is>
+      </c>
+      <c r="J58" s="4"/>
       <c r="K58" s="2"/>
     </row>
     <row r="59">
@@ -2747,28 +2758,32 @@
         </is>
       </c>
       <c r="C59" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E59" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F59" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I59" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
       <c r="J59" s="4"/>
       <c r="K59" s="2"/>
     </row>
@@ -2782,28 +2797,32 @@
         </is>
       </c>
       <c r="C60" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D60" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E60" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F60" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I60" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">났</t>
+        </is>
+      </c>
       <c r="J60" s="4"/>
       <c r="K60" s="2"/>
     </row>
@@ -2817,28 +2836,32 @@
         </is>
       </c>
       <c r="C61" s="2">
+        <v>6</v>
+      </c>
+      <c r="D61" s="2">
+        <v>6</v>
+      </c>
+      <c r="E61" s="2">
         <v>5</v>
       </c>
-      <c r="D61" s="2">
-        <v>5</v>
-      </c>
-      <c r="E61" s="2">
-        <v>12</v>
-      </c>
       <c r="F61" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–南</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I61" s="2"/>
+          <t xml:space="preserve">–南</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
+        </is>
+      </c>
       <c r="J61" s="4"/>
       <c r="K61" s="2"/>
     </row>
@@ -2858,27 +2881,32 @@
         <v>6</v>
       </c>
       <c r="E62" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F62" s="2">
-        <v>1</v>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">성</t>
-        </is>
-      </c>
-      <c r="J62" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|潢</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+潢</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲 아래 먹칠로 가려짐, 왼쪽 여백에 潢 → 仲|潢 추정</t>
+        </is>
+      </c>
       <c r="K62" s="2"/>
     </row>
     <row r="63">
@@ -2897,31 +2925,27 @@
         <v>6</v>
       </c>
       <c r="E63" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F63" s="2">
-        <v>1</v>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">해</t>
-        </is>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 해/화</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥</t>
+        </is>
+      </c>
+      <c r="J63" s="4"/>
       <c r="K63" s="2"/>
     </row>
     <row r="64">
@@ -2940,26 +2964,22 @@
         <v>6</v>
       </c>
       <c r="E64" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F64" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I64" s="2"/>
       <c r="J64" s="4"/>
       <c r="K64" s="2"/>
     </row>
@@ -2979,31 +2999,25 @@
         <v>6</v>
       </c>
       <c r="E65" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F65" s="2">
-        <v>2</v>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">났</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 았/났</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|無|南</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="I65" s="2"/>
+      <c r="J65" s="4"/>
       <c r="K65" s="2"/>
     </row>
     <row r="66">
@@ -3022,24 +3036,24 @@
         <v>6</v>
       </c>
       <c r="E66" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F66" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–南</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구</t>
+          <t xml:space="preserve">응</t>
         </is>
       </c>
       <c r="J66" s="4"/>
@@ -3061,26 +3075,22 @@
         <v>6</v>
       </c>
       <c r="E67" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F67" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I67" s="2"/>
       <c r="J67" s="4"/>
       <c r="K67" s="2"/>
     </row>
@@ -3100,175 +3110,28 @@
         <v>6</v>
       </c>
       <c r="E68" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F68" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흥</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I68" s="2"/>
       <c r="J68" s="4"/>
       <c r="K68" s="2"/>
     </row>
-    <row r="69">
-      <c r="A69" s="2">
-        <v>1</v>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/천안 삼거리.png</t>
-        </is>
-      </c>
-      <c r="C69" s="2">
-        <v>6</v>
-      </c>
-      <c r="D69" s="2">
-        <v>6</v>
-      </c>
-      <c r="E69" s="2">
-        <v>8</v>
-      </c>
-      <c r="F69" s="2">
-        <v>3</v>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I69" s="2"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="2"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2">
-        <v>1</v>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/천안 삼거리.png</t>
-        </is>
-      </c>
-      <c r="C70" s="2">
-        <v>6</v>
-      </c>
-      <c r="D70" s="2">
-        <v>6</v>
-      </c>
-      <c r="E70" s="2">
-        <v>9</v>
-      </c>
-      <c r="F70" s="2">
-        <v>3</v>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南無南</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南無南</t>
-        </is>
-      </c>
-      <c r="I70" s="3"/>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한 정간에 南·無·南 세로로 쌓여 쓰임</t>
-        </is>
-      </c>
-      <c r="K70" s="2"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2">
-        <v>1</v>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/천안 삼거리.png</t>
-        </is>
-      </c>
-      <c r="C71" s="2">
-        <v>6</v>
-      </c>
-      <c r="D71" s="2">
-        <v>6</v>
-      </c>
-      <c r="E71" s="2">
-        <v>10</v>
-      </c>
-      <c r="F71" s="2">
-        <v>4</v>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I71" s="2"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="2"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2">
-        <v>1</v>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-3/천안 삼거리.png</t>
-        </is>
-      </c>
-      <c r="C72" s="2">
-        <v>6</v>
-      </c>
-      <c r="D72" s="2">
-        <v>6</v>
-      </c>
-      <c r="E72" s="2">
-        <v>11</v>
-      </c>
-      <c r="F72" s="2">
-        <v>4</v>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I72" s="2"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K72"/>
+  <autoFilter ref="A1:K68"/>
 </worksheet>
 </file>
 
@@ -3293,7 +3156,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="29.14" customHeight="1">
+    <row r="2" ht="77.61" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3312,14 +3175,14 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="29.14" customHeight="1">
+    <row r="3" ht="77.61" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
@@ -3329,7 +3192,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -3339,9 +3202,9 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">척</t>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">축</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -3349,7 +3212,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I3" s="29" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
@@ -3359,7 +3222,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K3" s="29" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
@@ -3369,22 +3232,22 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M3" s="29" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">천</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="29.14" customHeight="1">
+    <row r="4" ht="77.61" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">해</t>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -3392,9 +3255,9 @@
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="E4" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구</t>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">루</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr">
@@ -3402,7 +3265,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
@@ -3412,7 +3275,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I4" s="32" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">멋</t>
         </is>
@@ -3422,7 +3285,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="32" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -3432,32 +3295,32 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M4" s="32" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="29.14" customHeight="1">
+    <row r="5" ht="77.61" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">와</t>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -3465,7 +3328,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="33" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3475,7 +3338,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I5" s="33" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -3485,22 +3348,26 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K5" s="33"/>
+      <c r="K5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
       <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M5" s="34"/>
-    </row>
-    <row r="6" ht="29.14" customHeight="1">
+      <c r="M5" s="27"/>
+    </row>
+    <row r="6" ht="77.61" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">났</t>
         </is>
@@ -3510,7 +3377,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -3520,7 +3387,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">졌</t>
         </is>
@@ -3530,7 +3397,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">겨</t>
         </is>
@@ -3540,7 +3407,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K6" s="29" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
@@ -3550,20 +3417,20 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M6" s="29" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="29.14" customHeight="1">
+    <row r="7" ht="77.61" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -3573,13 +3440,13 @@
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="E7" s="32"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="G7" s="32" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -3589,13 +3456,13 @@
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="I7" s="32"/>
+      <c r="I7" s="25"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="K7" s="32" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -3605,332 +3472,350 @@
           <t xml:space="preserve">–南</t>
         </is>
       </c>
-      <c r="M7" s="32" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="29.14" customHeight="1">
+    <row r="8" ht="77.61" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+潢</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+潢</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">워</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">워</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">은</t>
-        </is>
-      </c>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M8" s="33" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="29.14" customHeight="1">
+    <row r="9" ht="77.61" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K9" s="29" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흥</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="29.14" customHeight="1">
+    </row>
+    <row r="10" ht="77.61" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C10" s="32"/>
+      <c r="C10" s="25"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="E10" s="25"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="I10" s="28"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="M10" s="25"/>
+    </row>
+    <row r="11" ht="77.61" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="C11" s="26"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="32"/>
-      <c r="J10" s="21" t="inlineStr">
+      <c r="E11" s="26"/>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="G11" s="26"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+無
+南</t>
+        </is>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">흥</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K10" s="32"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="M10" s="32"/>
-    </row>
-    <row r="11" ht="29.14" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南無南</t>
-        </is>
-      </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南無南</t>
-        </is>
-      </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南無南</t>
-        </is>
-      </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I11" s="33"/>
-      <c r="J11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南無南</t>
-        </is>
-      </c>
-      <c r="K11" s="34"/>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M11" s="33"/>
-    </row>
-    <row r="12" ht="29.14" customHeight="1">
+      <c r="M11" s="26"/>
+    </row>
+    <row r="12" ht="77.61" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C12" s="29"/>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E12" s="29"/>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="29"/>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K12" s="29"/>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흥</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="29.14" customHeight="1">
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="77.61" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="32"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–無</t>
+        </is>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–無</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G13" s="32"/>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="I13" s="32"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K13" s="32"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–無</t>
-        </is>
-      </c>
-      <c r="M13" s="32"/>
-    </row>
-    <row r="14" ht="29.14" customHeight="1">
+      <c r="M13" s="25"/>
+    </row>
+    <row r="14" ht="77.61" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="33"/>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="C14" s="26"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G14" s="33"/>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="I14" s="33"/>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I14" s="26"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K14" s="33"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="K14" s="26"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無</t>
-        </is>
-      </c>
-      <c r="M14" s="33"/>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="M14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/천안 삼거리 (굿거리).xlsx
+++ b/sheets/민요/검수/천안 삼거리 (굿거리).xlsx
@@ -402,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 머리 "천안삼거리 "굿거리"". 손으로 그린 격자 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽부터 6줄 사용(왼쪽 빈 줄 제외). 가사는 각 율명 줄 오른쪽 칸. 7정간 흥·10정간 응은 후렴 입타령. 9정간 南|無|南, 12정간 潢|無 는 한 정간에 세로로 쌓여 쓰임. 줄6 6정간 아래 먹칠 번짐.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 머리 "천안삼거리 "굿거리"". 손으로 그린 격자 12정간, 굵은 선 3칸마다 → 3/4·12. 오른쪽부터 6줄 사용(왼쪽 빈 줄 제외). 가사는 각 율명 줄 오른쪽 칸. 7정간 흥·10정간 응은 후렴 입타령. 9정간 南|無|南, 12정간 潢|無 는 한 정간에 세로로 쌓여 쓰임. 줄6 6정간 아래 먹칠 번짐. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -2089,13 +2089,13 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|潢</t>
+          <t xml:space="preserve">仲|黃</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-潢</t>
+黃</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2888,13 +2888,13 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|潢</t>
+          <t xml:space="preserve">仲|黃</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-潢</t>
+黃</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲 아래 먹칠로 가려짐, 왼쪽 여백에 潢 → 仲|潢 추정</t>
+          <t xml:space="preserve">仲 아래 먹칠로 가려짐, 왼쪽 여백에 潢 → 仲|潢 추정; 黃/潢?</t>
         </is>
       </c>
       <c r="K62" s="2"/>
@@ -3483,7 +3483,7 @@
       <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-潢</t>
+黃</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -3504,7 +3504,7 @@
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-潢</t>
+黃</t>
         </is>
       </c>
       <c r="G8" s="26" t="inlineStr">
